--- a/Results/2-26-2026/Design Optimization Results/Local_Refinement_Results.xlsx
+++ b/Results/2-26-2026/Design Optimization Results/Local_Refinement_Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Bio-Inspired-Sensing/Results/2-26-2026/Design Optimization Results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="11_514DC117090FA1FFAF4FB7A7E0012D16118B317C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7902486C-9B9E-4883-A0B4-7B1958E5C3B8}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_514DC117090FA1FFAF4FB7A7E0012D16118B317C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6BF7312-2237-42F3-BF82-B4A637E718EF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1697,6 +1697,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
